--- a/data/gold/results/steenmeijer_table.xlsx
+++ b/data/gold/results/steenmeijer_table.xlsx
@@ -64,97 +64,97 @@
     <t>Bottom-up</t>
   </si>
   <si>
-    <t>4,815 (100·0%)</t>
-  </si>
-  <si>
-    <t>3,294 (68·4%)</t>
-  </si>
-  <si>
-    <t>756 (15·7%)</t>
-  </si>
-  <si>
-    <t>181 (3·8%)</t>
-  </si>
-  <si>
-    <t>10 (0·2%)</t>
-  </si>
-  <si>
-    <t>35 (0·7%)</t>
-  </si>
-  <si>
-    <t>540 (11·2%)</t>
-  </si>
-  <si>
-    <t>2,601 (100·0%)</t>
-  </si>
-  <si>
-    <t>1,309 (50·3%)</t>
-  </si>
-  <si>
-    <t>1,132 (43·5%)</t>
-  </si>
-  <si>
-    <t>135 (5·2%)</t>
+    <t>4,875 (100·0%)</t>
+  </si>
+  <si>
+    <t>1,983 (40·7%)</t>
+  </si>
+  <si>
+    <t>1,340 (27·5%)</t>
+  </si>
+  <si>
+    <t>921 (18·9%)</t>
+  </si>
+  <si>
+    <t>13 (0·3%)</t>
+  </si>
+  <si>
+    <t>12 (0·2%)</t>
+  </si>
+  <si>
+    <t>606 (12·4%)</t>
+  </si>
+  <si>
+    <t>5,595 (100·0%)</t>
+  </si>
+  <si>
+    <t>1,862 (33·3%)</t>
+  </si>
+  <si>
+    <t>2,924 (52·3%)</t>
+  </si>
+  <si>
+    <t>782 (14·0%)</t>
   </si>
   <si>
     <t>0 (&lt;0·1%)</t>
   </si>
   <si>
-    <t>25 (0·9%)</t>
-  </si>
-  <si>
-    <t>47 (100·0%)</t>
-  </si>
-  <si>
-    <t>27 (58·2%)</t>
-  </si>
-  <si>
-    <t>17 (36·8%)</t>
-  </si>
-  <si>
-    <t>2 (4·7%)</t>
+    <t>28 (0·5%)</t>
+  </si>
+  <si>
+    <t>43 (100·0%)</t>
+  </si>
+  <si>
+    <t>16 (37·7%)</t>
+  </si>
+  <si>
+    <t>20 (46·6%)</t>
+  </si>
+  <si>
+    <t>7 (15·2%)</t>
   </si>
   <si>
     <t>0 (0·4%)</t>
   </si>
   <si>
-    <t>2,753 (100·0%)</t>
-  </si>
-  <si>
-    <t>1,884 (68·4%)</t>
-  </si>
-  <si>
-    <t>755 (27·4%)</t>
-  </si>
-  <si>
-    <t>113 (4·1%)</t>
+    <t>3,833 (100·0%)</t>
+  </si>
+  <si>
+    <t>1,654 (43·1%)</t>
+  </si>
+  <si>
+    <t>1,647 (43·0%)</t>
+  </si>
+  <si>
+    <t>531 (13·9%)</t>
   </si>
   <si>
     <t>2 (&lt;0·1%)</t>
   </si>
   <si>
-    <t>840 (100·0%)</t>
-  </si>
-  <si>
-    <t>562 (66·8%)</t>
-  </si>
-  <si>
-    <t>221 (26·3%)</t>
-  </si>
-  <si>
-    <t>57 (6·8%)</t>
-  </si>
-  <si>
-    <t>25,857 (100·0%)</t>
-  </si>
-  <si>
-    <t>23,221 (89·8%)</t>
-  </si>
-  <si>
-    <t>1,735 (6·7%)</t>
-  </si>
-  <si>
-    <t>901 (3·5%)</t>
+    <t>1,482 (100·0%)</t>
+  </si>
+  <si>
+    <t>551 (37·2%)</t>
+  </si>
+  <si>
+    <t>701 (47·3%)</t>
+  </si>
+  <si>
+    <t>230 (15·5%)</t>
+  </si>
+  <si>
+    <t>40,597 (100·0%)</t>
+  </si>
+  <si>
+    <t>37,552 (92·5%)</t>
+  </si>
+  <si>
+    <t>1,950 (4·8%)</t>
+  </si>
+  <si>
+    <t>1,094 (2·7%)</t>
   </si>
   <si>
     <t>NA</t>
@@ -164,16 +164,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -189,7 +181,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -197,30 +189,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,30 +493,30 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -568,7 +542,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
@@ -594,7 +568,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
@@ -620,7 +594,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
@@ -646,7 +620,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
@@ -672,7 +646,7 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
@@ -698,7 +672,7 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
